--- a/employment_forms/029_part_time_employment_contract_form--employment_forms.xlsx
+++ b/employment_forms/029_part_time_employment_contract_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>employment_details</t>
+          <t>Employment Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contract_type</t>
+          <t>Contract Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pay_frequency</t>
+          <t>Pay Frequency</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pay_rate</t>
+          <t>Pay Rate</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pay_rate_frequency</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pay_rate_frequency</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_description</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Job Description</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_responsibilities</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>Job Responsibilities</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>job_responsibilities</t>
+          <t>employee_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>job_responsibilities</t>
+          <t>Employee Status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>employee_status</t>
+          <t>employee_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>employee_status</t>
+          <t>Employee Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_type</t>
+          <t>work_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>employee_type</t>
+          <t>Work Location</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>work_hours</t>
+          <t>job_category</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>work_hours</t>
+          <t>Job Category</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>work_location</t>
+          <t>work_hours</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>work_location</t>
+          <t>Work Hours</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>job_category</t>
+          <t>employment_terms</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Job Category</t>
+          <t>Employment Terms</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>job_category</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>job_category</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>work_frequency</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>work_frequency</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>work_frequency</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>work_frequency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>pay_rate</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pay_rate</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>pay_rate</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>pay_rate</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>work_frequency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>work_frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>job_responsibilities</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>job_responsibilities</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_type</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>employee_type</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>work_location</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>work_location</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>employment_terms</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>employment_terms</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1148,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'seasonal'}</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Seasonal'}</t>
+          <t>Seasonal</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1199,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'on_leave'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'On Leave'}</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
@@ -1216,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'terminated'}</t>
+          <t>terminated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Terminated'}</t>
+          <t>Terminated</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1267,114 +1037,114 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'seasonal'}</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Seasonal'}</t>
+          <t>Seasonal</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>work_location_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>work_location_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>work_location_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'saturday'}</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday'}</t>
+          <t>Seasonal</t>
         </is>
       </c>
     </row>
@@ -1386,267 +1156,114 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'sunday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>work_location_choices</t>
+          <t>work_hours_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'on-site'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'On-site'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>work_location_choices</t>
+          <t>work_hours_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'remote'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Remote'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_location_choices</t>
+          <t>work_hours_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>work_hours_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>work_hours_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>work_hours_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'seasonal'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Seasonal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'label':_'full-time'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'label': 'Full-time'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'label':_'part-time'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'label': 'Part-time'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'label':_'seasonal'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'label': 'Seasonal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>employee_type_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'label':_'part-time'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'label': 'Part-time'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>employee_type_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'label':_'full-time'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'label': 'Full-time'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>employee_type_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'label':_'seasonal'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'label': 'Seasonal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>work_location_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'label':_'on-site'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'label': 'On-site'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>work_location_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'remote'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'Remote'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>work_location_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'hybrid'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'Hybrid'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
